--- a/membership_application_form_templates/009_country_club_seasonal_membership_application--membership_application_form_templates.xlsx
+++ b/membership_application_form_templates/009_country_club_seasonal_membership_application--membership_application_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'basic',_'value':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Basic', 'value': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'premium',_'value':_'premium'}</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Premium', 'value': 'Premium'}</t>
+          <t>Premium</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'vip',_'value':_'vip'}</t>
+          <t>vip</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'VIP', 'value': 'VIP'}</t>
+          <t>VIP</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'i_have_read_and_agreed_to_the_terms_and_conditions',_'value':_'i_have_read_and_agreed_to_the_terms_and_conditions'}</t>
+          <t>i_have_read_and_agreed_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'I have read and agreed to the terms and conditions', 'value': 'I have read and agreed to the terms and conditions'}</t>
+          <t>I have read and agreed to the terms and conditions</t>
         </is>
       </c>
     </row>
